--- a/p6_deployment/data/england/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/england/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,161 +448,705 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>jXP8f29S</t>
+          <t>Kl1AOZN9</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="C2" t="n">
-        <v>7.5</v>
+        <v>4.33</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>htCzjMHq</t>
+          <t>t4kJMDhM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="D3" t="n">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z51uktXk</t>
+          <t>CntkHiGq</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>nu5ql0nd</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0rgRCqPd</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6.25</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vZiVB3v3</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="C7" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dAnzBNg9</t>
+          <t>nHdPI4il</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.14</v>
+        <v>2.6</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>z1ovAs9F</t>
+          <t>8WpYGrM0</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="C9" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Sd97hFwr</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.07</v>
+        <v>5.75</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>5.25</v>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>t0DBiZhl</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D24" t="n">
         <v>7</v>
       </c>
-      <c r="C11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.33</v>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4.75</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/england/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/england/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,30 +576,30 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.75</v>
+        <v>4.1</v>
       </c>
       <c r="C10" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="D11" t="n">
         <v>1.67</v>
@@ -608,544 +608,576 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.53</v>
+        <v>5.25</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="C13" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="C14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="C15" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="C16" t="n">
         <v>3.6</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9</v>
+        <v>1.65</v>
       </c>
       <c r="C17" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D17" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="C18" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="C19" t="n">
         <v>3.6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
         <v>3.75</v>
       </c>
       <c r="D20" t="n">
-        <v>5.5</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="C21" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D21" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.33</v>
+        <v>1.6</v>
       </c>
       <c r="C22" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D22" t="n">
-        <v>1.8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="C23" t="n">
         <v>3.4</v>
       </c>
       <c r="D23" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.57</v>
+        <v>4.33</v>
       </c>
       <c r="C24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="C25" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="C26" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D26" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D27" t="n">
         <v>1.57</v>
-      </c>
-      <c r="C27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D27" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="C28" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="D28" t="n">
-        <v>6.5</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="C29" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D29" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="C30" t="n">
         <v>4.33</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="C31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D31" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="C32" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="D32" t="n">
-        <v>2.88</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="C33" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D33" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="C34" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>2.3</v>
       </c>
       <c r="C35" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D35" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="C36" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="C37" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="C38" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D38" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.5</v>
+        <v>1.44</v>
       </c>
       <c r="C39" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="C40" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="C41" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D41" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="C42" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="D42" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="C43" t="n">
         <v>3.4</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B47" t="n">
         <v>1.67</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C47" t="n">
         <v>4</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D47" t="n">
         <v>4.75</v>
       </c>
     </row>

--- a/p6_deployment/data/england/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/england/data_preparation/format_data/df_match_odds_form.xlsx
@@ -487,7 +487,7 @@
         <v>1.22</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="C5" t="n">
         <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="6">
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="D6" t="n">
         <v>8.5</v>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="C12" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="D12" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C13" t="n">
         <v>3.8</v>
@@ -647,10 +647,10 @@
         <v>1.5</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="15">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="C26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="27">
@@ -1162,7 +1162,7 @@
         <v>4.1</v>
       </c>
       <c r="D46" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="47">

--- a/p6_deployment/data/england/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/england/data_preparation/format_data/df_match_odds_form.xlsx
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="C9" t="n">
         <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="10">
@@ -618,7 +618,7 @@
         <v>4.75</v>
       </c>
       <c r="D12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="13">
